--- a/ig/DM-SEPTEMBRE-2026/ValueSet-jdv-localisation-anatomique-cisis.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/ValueSet-jdv-localisation-anatomique-cisis.xlsx
@@ -54,7 +54,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>retired</t>
   </si>
   <si>
     <t>Experimental</t>
